--- a/predictions.xlsx
+++ b/predictions.xlsx
@@ -453,7 +453,7 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -477,7 +477,7 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -533,7 +533,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -557,7 +557,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -565,7 +565,7 @@
         <v>0</v>
       </c>
       <c r="B17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -573,7 +573,7 @@
         <v>0</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -581,7 +581,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -597,7 +597,7 @@
         <v>0</v>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -629,7 +629,7 @@
         <v>0</v>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -637,7 +637,7 @@
         <v>0</v>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -645,7 +645,7 @@
         <v>0</v>
       </c>
       <c r="B27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="B29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -677,7 +677,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -685,7 +685,7 @@
         <v>0</v>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -693,7 +693,7 @@
         <v>0</v>
       </c>
       <c r="B33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -701,7 +701,7 @@
         <v>0</v>
       </c>
       <c r="B34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -709,7 +709,7 @@
         <v>0</v>
       </c>
       <c r="B35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -741,7 +741,7 @@
         <v>0</v>
       </c>
       <c r="B39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -781,7 +781,7 @@
         <v>0</v>
       </c>
       <c r="B44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -789,7 +789,7 @@
         <v>0</v>
       </c>
       <c r="B45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -805,7 +805,7 @@
         <v>0</v>
       </c>
       <c r="B47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -813,7 +813,7 @@
         <v>0</v>
       </c>
       <c r="B48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -829,7 +829,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -837,7 +837,7 @@
         <v>0</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -845,7 +845,7 @@
         <v>0</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -853,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -861,7 +861,7 @@
         <v>0</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -885,7 +885,7 @@
         <v>0</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -901,7 +901,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -909,7 +909,7 @@
         <v>0</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -933,7 +933,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -957,7 +957,7 @@
         <v>0</v>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -973,7 +973,7 @@
         <v>0</v>
       </c>
       <c r="B68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="B69" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -989,7 +989,7 @@
         <v>0</v>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -1029,7 +1029,7 @@
         <v>0</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -1053,7 +1053,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -1061,7 +1061,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1085,7 +1085,7 @@
         <v>0</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -1133,7 +1133,7 @@
         <v>0</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -1157,7 +1157,7 @@
         <v>0</v>
       </c>
       <c r="B91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="92">
@@ -1189,7 +1189,7 @@
         <v>0</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -1221,7 +1221,7 @@
         <v>0</v>
       </c>
       <c r="B99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100">
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="B101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -1245,7 +1245,7 @@
         <v>0</v>
       </c>
       <c r="B102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -1253,7 +1253,7 @@
         <v>0</v>
       </c>
       <c r="B103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -1285,7 +1285,7 @@
         <v>0</v>
       </c>
       <c r="B107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="108">
@@ -1293,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="B108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="B113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="B114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -1349,7 +1349,7 @@
         <v>0</v>
       </c>
       <c r="B115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="116">
@@ -1357,7 +1357,7 @@
         <v>0</v>
       </c>
       <c r="B116" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -1381,7 +1381,7 @@
         <v>0</v>
       </c>
       <c r="B119" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120">
@@ -1389,7 +1389,7 @@
         <v>0</v>
       </c>
       <c r="B120" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="B122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="123">
@@ -1445,7 +1445,7 @@
         <v>0</v>
       </c>
       <c r="B127" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128">
@@ -1453,7 +1453,7 @@
         <v>0</v>
       </c>
       <c r="B128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -1461,7 +1461,7 @@
         <v>0</v>
       </c>
       <c r="B129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="130">
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="B130" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131">
@@ -1477,7 +1477,7 @@
         <v>0</v>
       </c>
       <c r="B131" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -1485,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="133">
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="B136" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137">
@@ -1533,7 +1533,7 @@
         <v>0</v>
       </c>
       <c r="B138" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="B139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -1573,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="B143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="144">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="B144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145">
@@ -1589,7 +1589,7 @@
         <v>0</v>
       </c>
       <c r="B145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146">
@@ -1597,7 +1597,7 @@
         <v>0</v>
       </c>
       <c r="B146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147">
@@ -1605,7 +1605,7 @@
         <v>0</v>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -1613,7 +1613,7 @@
         <v>0</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149">
@@ -1621,7 +1621,7 @@
         <v>0</v>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150">
@@ -1637,7 +1637,7 @@
         <v>0</v>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152">
@@ -1669,7 +1669,7 @@
         <v>0</v>
       </c>
       <c r="B155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156">
@@ -1685,7 +1685,7 @@
         <v>0</v>
       </c>
       <c r="B157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -1693,7 +1693,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="159">
@@ -1701,7 +1701,7 @@
         <v>0</v>
       </c>
       <c r="B159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160">
@@ -1709,7 +1709,7 @@
         <v>0</v>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="161">
@@ -1717,7 +1717,7 @@
         <v>0</v>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162">
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
       <c r="B163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164">
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="B165" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="166">
@@ -1765,7 +1765,7 @@
         <v>0</v>
       </c>
       <c r="B167" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="168">
@@ -1773,7 +1773,7 @@
         <v>0</v>
       </c>
       <c r="B168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
       <c r="B169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="170">
@@ -1797,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="172">
@@ -1813,7 +1813,7 @@
         <v>0</v>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="174">
@@ -1821,7 +1821,7 @@
         <v>0</v>
       </c>
       <c r="B174" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="175">
@@ -1837,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="B176" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="177">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179">
@@ -1861,7 +1861,7 @@
         <v>0</v>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="180">
@@ -1869,7 +1869,7 @@
         <v>0</v>
       </c>
       <c r="B180" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="181">
@@ -1901,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="B184" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185">
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="B185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="186">
@@ -1933,7 +1933,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="189">
@@ -1941,7 +1941,7 @@
         <v>0</v>
       </c>
       <c r="B189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="190">
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="B191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="192">
@@ -1973,7 +1973,7 @@
         <v>0</v>
       </c>
       <c r="B193" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="194">
@@ -1981,7 +1981,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="195">
@@ -1989,7 +1989,7 @@
         <v>0</v>
       </c>
       <c r="B195" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="196">
@@ -2021,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="B199" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="200">
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="B202" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="203">
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
       <c r="B203" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="204">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -2069,7 +2069,7 @@
         <v>0</v>
       </c>
       <c r="B205" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="206">
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="B208" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="209">
@@ -2109,7 +2109,7 @@
         <v>0</v>
       </c>
       <c r="B210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -2117,7 +2117,7 @@
         <v>0</v>
       </c>
       <c r="B211" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="212">
@@ -2125,7 +2125,7 @@
         <v>0</v>
       </c>
       <c r="B212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="213">
@@ -2133,7 +2133,7 @@
         <v>0</v>
       </c>
       <c r="B213" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="214">
@@ -2141,7 +2141,7 @@
         <v>0</v>
       </c>
       <c r="B214" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215">
@@ -2149,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="B215" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216">
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="217">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="B217" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="218">
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="B218" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="219">
@@ -2189,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="221">
@@ -2229,7 +2229,7 @@
         <v>0</v>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -2245,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -2253,7 +2253,7 @@
         <v>0</v>
       </c>
       <c r="B228" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="B231" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -2293,7 +2293,7 @@
         <v>0</v>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -2301,7 +2301,7 @@
         <v>0</v>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="235">
@@ -2317,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="237">
@@ -2341,7 +2341,7 @@
         <v>0</v>
       </c>
       <c r="B239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
@@ -2357,7 +2357,7 @@
         <v>0</v>
       </c>
       <c r="B241" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="244">
@@ -2389,7 +2389,7 @@
         <v>0</v>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -2421,7 +2421,7 @@
         <v>0</v>
       </c>
       <c r="B249" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -2445,7 +2445,7 @@
         <v>0</v>
       </c>
       <c r="B252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -2453,7 +2453,7 @@
         <v>0</v>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="254">
@@ -2461,7 +2461,7 @@
         <v>0</v>
       </c>
       <c r="B254" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="255">
@@ -2469,7 +2469,7 @@
         <v>0</v>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="257">
@@ -2493,7 +2493,7 @@
         <v>0</v>
       </c>
       <c r="B258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -2509,7 +2509,7 @@
         <v>0</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="261">
@@ -2517,7 +2517,7 @@
         <v>0</v>
       </c>
       <c r="B261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="262">
@@ -2525,7 +2525,7 @@
         <v>0</v>
       </c>
       <c r="B262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264">
@@ -2541,7 +2541,7 @@
         <v>0</v>
       </c>
       <c r="B264" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="265">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270">
@@ -2589,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="B270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="B271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="272">
@@ -2605,7 +2605,7 @@
         <v>0</v>
       </c>
       <c r="B272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
       <c r="B273" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="274">
@@ -2629,7 +2629,7 @@
         <v>0</v>
       </c>
       <c r="B275" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="276">
@@ -2637,7 +2637,7 @@
         <v>0</v>
       </c>
       <c r="B276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="278">
@@ -2653,7 +2653,7 @@
         <v>0</v>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -2661,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="B279" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -2669,7 +2669,7 @@
         <v>0</v>
       </c>
       <c r="B280" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -2693,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="B283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="284">
@@ -2701,7 +2701,7 @@
         <v>0</v>
       </c>
       <c r="B284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
@@ -2733,7 +2733,7 @@
         <v>0</v>
       </c>
       <c r="B288" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="289">
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="290">
@@ -2749,7 +2749,7 @@
         <v>0</v>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -2757,7 +2757,7 @@
         <v>0</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="292">
@@ -2765,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="B292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
@@ -2773,7 +2773,7 @@
         <v>0</v>
       </c>
       <c r="B293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="294">
@@ -2797,7 +2797,7 @@
         <v>0</v>
       </c>
       <c r="B296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="B299" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
@@ -2837,7 +2837,7 @@
         <v>0</v>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
@@ -2861,7 +2861,7 @@
         <v>0</v>
       </c>
       <c r="B304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -2869,7 +2869,7 @@
         <v>0</v>
       </c>
       <c r="B305" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
@@ -2901,7 +2901,7 @@
         <v>0</v>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="310">
@@ -2909,7 +2909,7 @@
         <v>0</v>
       </c>
       <c r="B310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -2917,7 +2917,7 @@
         <v>0</v>
       </c>
       <c r="B311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -2925,7 +2925,7 @@
         <v>0</v>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="313">
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316">
@@ -2965,7 +2965,7 @@
         <v>0</v>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
@@ -2989,7 +2989,7 @@
         <v>0</v>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321">
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="322">
@@ -3021,7 +3021,7 @@
         <v>0</v>
       </c>
       <c r="B324" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
@@ -3029,7 +3029,7 @@
         <v>0</v>
       </c>
       <c r="B325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326">
@@ -3045,7 +3045,7 @@
         <v>0</v>
       </c>
       <c r="B327" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328">
@@ -3077,7 +3077,7 @@
         <v>0</v>
       </c>
       <c r="B331" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -3085,7 +3085,7 @@
         <v>0</v>
       </c>
       <c r="B332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333">
@@ -3093,7 +3093,7 @@
         <v>0</v>
       </c>
       <c r="B333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="334">
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -3117,7 +3117,7 @@
         <v>0</v>
       </c>
       <c r="B336" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
@@ -3133,7 +3133,7 @@
         <v>0</v>
       </c>
       <c r="B338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
@@ -3141,7 +3141,7 @@
         <v>0</v>
       </c>
       <c r="B339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340">
@@ -3181,7 +3181,7 @@
         <v>0</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="B347" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="348">
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="349">
@@ -3221,7 +3221,7 @@
         <v>0</v>
       </c>
       <c r="B349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -3229,7 +3229,7 @@
         <v>0</v>
       </c>
       <c r="B350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351">
@@ -3261,7 +3261,7 @@
         <v>0</v>
       </c>
       <c r="B354" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -3269,7 +3269,7 @@
         <v>0</v>
       </c>
       <c r="B355" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
@@ -3301,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="B359" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="360">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="B360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -3317,7 +3317,7 @@
         <v>0</v>
       </c>
       <c r="B361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -3325,7 +3325,7 @@
         <v>0</v>
       </c>
       <c r="B362" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="363">
@@ -3333,7 +3333,7 @@
         <v>0</v>
       </c>
       <c r="B363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -3357,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="B366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
       <c r="B369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="370">
@@ -3405,7 +3405,7 @@
         <v>0</v>
       </c>
       <c r="B372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="374">
@@ -3421,7 +3421,7 @@
         <v>0</v>
       </c>
       <c r="B374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="375">
@@ -3429,7 +3429,7 @@
         <v>0</v>
       </c>
       <c r="B375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
@@ -3437,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="B376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
       <c r="B378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
@@ -3469,7 +3469,7 @@
         <v>0</v>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="381">
@@ -3477,7 +3477,7 @@
         <v>0</v>
       </c>
       <c r="B381" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
@@ -3501,7 +3501,7 @@
         <v>0</v>
       </c>
       <c r="B384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="385">
@@ -3509,7 +3509,7 @@
         <v>0</v>
       </c>
       <c r="B385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="386">
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
       <c r="B387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -3533,7 +3533,7 @@
         <v>0</v>
       </c>
       <c r="B388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
@@ -3541,7 +3541,7 @@
         <v>0</v>
       </c>
       <c r="B389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="390">
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="B390" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="391">
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="B393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="394">
@@ -3581,7 +3581,7 @@
         <v>0</v>
       </c>
       <c r="B394" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -3597,7 +3597,7 @@
         <v>0</v>
       </c>
       <c r="B396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
@@ -3605,7 +3605,7 @@
         <v>0</v>
       </c>
       <c r="B397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="B399" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="400">
@@ -3629,7 +3629,7 @@
         <v>0</v>
       </c>
       <c r="B400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="401">
@@ -3653,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="B403" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="404">
@@ -3661,7 +3661,7 @@
         <v>0</v>
       </c>
       <c r="B404" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="405">
@@ -3685,7 +3685,7 @@
         <v>0</v>
       </c>
       <c r="B407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -3701,7 +3701,7 @@
         <v>0</v>
       </c>
       <c r="B409" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="410">
@@ -3709,7 +3709,7 @@
         <v>0</v>
       </c>
       <c r="B410" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="411">
@@ -3717,7 +3717,7 @@
         <v>0</v>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412">
@@ -3733,7 +3733,7 @@
         <v>0</v>
       </c>
       <c r="B413" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -3757,7 +3757,7 @@
         <v>0</v>
       </c>
       <c r="B416" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="417">
@@ -3765,7 +3765,7 @@
         <v>0</v>
       </c>
       <c r="B417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="418">
@@ -3773,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="B418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -3781,7 +3781,7 @@
         <v>0</v>
       </c>
       <c r="B419" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="420">
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="B422" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="B425" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="426">
@@ -3845,7 +3845,7 @@
         <v>0</v>
       </c>
       <c r="B427" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="428">
@@ -3853,7 +3853,7 @@
         <v>0</v>
       </c>
       <c r="B428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -3861,7 +3861,7 @@
         <v>0</v>
       </c>
       <c r="B429" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="430">
@@ -3869,7 +3869,7 @@
         <v>0</v>
       </c>
       <c r="B430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -3893,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="B433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
@@ -3909,7 +3909,7 @@
         <v>0</v>
       </c>
       <c r="B435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -3925,7 +3925,7 @@
         <v>0</v>
       </c>
       <c r="B437" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="B438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="439">
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="B439" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
       <c r="B444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
@@ -3989,7 +3989,7 @@
         <v>0</v>
       </c>
       <c r="B445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="446">
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="B446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
@@ -4005,7 +4005,7 @@
         <v>0</v>
       </c>
       <c r="B447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="B450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="B451" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -4053,7 +4053,7 @@
         <v>0</v>
       </c>
       <c r="B453" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="B457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="458">
@@ -4101,7 +4101,7 @@
         <v>0</v>
       </c>
       <c r="B459" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="460">
@@ -4117,7 +4117,7 @@
         <v>0</v>
       </c>
       <c r="B461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="B464" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -4157,7 +4157,7 @@
         <v>0</v>
       </c>
       <c r="B466" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="467">
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
       <c r="B468" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="469">
@@ -4189,7 +4189,7 @@
         <v>0</v>
       </c>
       <c r="B470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -4197,7 +4197,7 @@
         <v>0</v>
       </c>
       <c r="B471" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
@@ -4205,7 +4205,7 @@
         <v>0</v>
       </c>
       <c r="B472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="B473" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474">
@@ -4221,7 +4221,7 @@
         <v>0</v>
       </c>
       <c r="B474" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -4229,7 +4229,7 @@
         <v>0</v>
       </c>
       <c r="B475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476">
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="B477" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478">
@@ -4277,7 +4277,7 @@
         <v>0</v>
       </c>
       <c r="B481" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482">
@@ -4293,7 +4293,7 @@
         <v>0</v>
       </c>
       <c r="B483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="484">
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485">
@@ -4309,7 +4309,7 @@
         <v>0</v>
       </c>
       <c r="B485" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486">
@@ -4317,7 +4317,7 @@
         <v>0</v>
       </c>
       <c r="B486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="B490" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="491">
@@ -4373,7 +4373,7 @@
         <v>0</v>
       </c>
       <c r="B493" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -4389,7 +4389,7 @@
         <v>0</v>
       </c>
       <c r="B495" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="496">
@@ -4397,7 +4397,7 @@
         <v>0</v>
       </c>
       <c r="B496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="497">
@@ -4405,7 +4405,7 @@
         <v>0</v>
       </c>
       <c r="B497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
       <c r="B499" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
@@ -4429,7 +4429,7 @@
         <v>0</v>
       </c>
       <c r="B500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -4437,7 +4437,7 @@
         <v>0</v>
       </c>
       <c r="B501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
@@ -4445,7 +4445,7 @@
         <v>0</v>
       </c>
       <c r="B502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="503">
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="B503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="504">
@@ -4485,7 +4485,7 @@
         <v>0</v>
       </c>
       <c r="B507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="508">
@@ -4509,7 +4509,7 @@
         <v>0</v>
       </c>
       <c r="B510" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="511">
@@ -4517,7 +4517,7 @@
         <v>0</v>
       </c>
       <c r="B511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512">
@@ -4525,7 +4525,7 @@
         <v>0</v>
       </c>
       <c r="B512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="513">
@@ -4533,7 +4533,7 @@
         <v>0</v>
       </c>
       <c r="B513" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -4541,7 +4541,7 @@
         <v>0</v>
       </c>
       <c r="B514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="515">
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="B516" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="517">
@@ -4565,7 +4565,7 @@
         <v>0</v>
       </c>
       <c r="B517" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
@@ -4573,7 +4573,7 @@
         <v>0</v>
       </c>
       <c r="B518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -4589,7 +4589,7 @@
         <v>0</v>
       </c>
       <c r="B520" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="521">
@@ -4597,7 +4597,7 @@
         <v>0</v>
       </c>
       <c r="B521" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522">
@@ -4613,7 +4613,7 @@
         <v>0</v>
       </c>
       <c r="B523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
@@ -4637,7 +4637,7 @@
         <v>0</v>
       </c>
       <c r="B526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
@@ -4653,7 +4653,7 @@
         <v>0</v>
       </c>
       <c r="B528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="529">
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="B529" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="B531" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="532">
@@ -4693,7 +4693,7 @@
         <v>0</v>
       </c>
       <c r="B533" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="534">
@@ -4701,7 +4701,7 @@
         <v>0</v>
       </c>
       <c r="B534" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -4709,7 +4709,7 @@
         <v>0</v>
       </c>
       <c r="B535" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="536">
@@ -4717,7 +4717,7 @@
         <v>0</v>
       </c>
       <c r="B536" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -4725,7 +4725,7 @@
         <v>0</v>
       </c>
       <c r="B537" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -4749,7 +4749,7 @@
         <v>0</v>
       </c>
       <c r="B540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="B542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="543">
@@ -4773,7 +4773,7 @@
         <v>0</v>
       </c>
       <c r="B543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -4781,7 +4781,7 @@
         <v>0</v>
       </c>
       <c r="B544" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -4805,7 +4805,7 @@
         <v>0</v>
       </c>
       <c r="B547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
@@ -4813,7 +4813,7 @@
         <v>0</v>
       </c>
       <c r="B548" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
@@ -4829,7 +4829,7 @@
         <v>0</v>
       </c>
       <c r="B550" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551">
@@ -4837,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="B551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
@@ -4845,7 +4845,7 @@
         <v>0</v>
       </c>
       <c r="B552" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="553">
@@ -4861,7 +4861,7 @@
         <v>0</v>
       </c>
       <c r="B554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="555">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="B555" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
@@ -4877,7 +4877,7 @@
         <v>0</v>
       </c>
       <c r="B556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="557">
@@ -4885,7 +4885,7 @@
         <v>0</v>
       </c>
       <c r="B557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -4893,7 +4893,7 @@
         <v>0</v>
       </c>
       <c r="B558" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
@@ -4901,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="B559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -4917,7 +4917,7 @@
         <v>0</v>
       </c>
       <c r="B561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562">
@@ -4925,7 +4925,7 @@
         <v>0</v>
       </c>
       <c r="B562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563">
@@ -4933,7 +4933,7 @@
         <v>0</v>
       </c>
       <c r="B563" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564">
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="B564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565">
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="B568" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569">
@@ -5045,7 +5045,7 @@
         <v>0</v>
       </c>
       <c r="B577" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="578">
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="B579" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="580">
@@ -5069,7 +5069,7 @@
         <v>0</v>
       </c>
       <c r="B580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581">
@@ -5093,7 +5093,7 @@
         <v>0</v>
       </c>
       <c r="B583" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584">
@@ -5101,7 +5101,7 @@
         <v>0</v>
       </c>
       <c r="B584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="B586" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587">
@@ -5125,7 +5125,7 @@
         <v>0</v>
       </c>
       <c r="B587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -5149,7 +5149,7 @@
         <v>0</v>
       </c>
       <c r="B590" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="591">
@@ -5157,7 +5157,7 @@
         <v>0</v>
       </c>
       <c r="B591" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="592">
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="B594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="B596" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="597">
@@ -5205,7 +5205,7 @@
         <v>0</v>
       </c>
       <c r="B597" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="598">
@@ -5213,7 +5213,7 @@
         <v>0</v>
       </c>
       <c r="B598" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="599">
@@ -5221,7 +5221,7 @@
         <v>0</v>
       </c>
       <c r="B599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
@@ -5253,7 +5253,7 @@
         <v>0</v>
       </c>
       <c r="B603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="604">
@@ -5293,7 +5293,7 @@
         <v>0</v>
       </c>
       <c r="B608" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="609">
@@ -5301,7 +5301,7 @@
         <v>0</v>
       </c>
       <c r="B609" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="610">
@@ -5309,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="B610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
@@ -5341,7 +5341,7 @@
         <v>0</v>
       </c>
       <c r="B614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
@@ -5357,7 +5357,7 @@
         <v>0</v>
       </c>
       <c r="B616" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="617">
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="B617" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="B618" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="B620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621">
@@ -5405,7 +5405,7 @@
         <v>0</v>
       </c>
       <c r="B622" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -5413,7 +5413,7 @@
         <v>0</v>
       </c>
       <c r="B623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -5421,7 +5421,7 @@
         <v>0</v>
       </c>
       <c r="B624" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="625">
@@ -5469,7 +5469,7 @@
         <v>0</v>
       </c>
       <c r="B630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="631">
@@ -5493,7 +5493,7 @@
         <v>0</v>
       </c>
       <c r="B633" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -5509,7 +5509,7 @@
         <v>0</v>
       </c>
       <c r="B635" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="636">
@@ -5525,7 +5525,7 @@
         <v>0</v>
       </c>
       <c r="B637" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="638">
@@ -5533,7 +5533,7 @@
         <v>0</v>
       </c>
       <c r="B638" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="639">
@@ -5589,7 +5589,7 @@
         <v>0</v>
       </c>
       <c r="B645" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="646">
@@ -5597,7 +5597,7 @@
         <v>0</v>
       </c>
       <c r="B646" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="647">
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="B648" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="B652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653">
@@ -5669,7 +5669,7 @@
         <v>0</v>
       </c>
       <c r="B655" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="656">
@@ -5677,7 +5677,7 @@
         <v>0</v>
       </c>
       <c r="B656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="657">
@@ -5685,7 +5685,7 @@
         <v>0</v>
       </c>
       <c r="B657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658">
@@ -5693,7 +5693,7 @@
         <v>0</v>
       </c>
       <c r="B658" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659">
@@ -5701,7 +5701,7 @@
         <v>0</v>
       </c>
       <c r="B659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -5709,7 +5709,7 @@
         <v>0</v>
       </c>
       <c r="B660" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661">
@@ -5725,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="B662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="B664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="B665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
@@ -5757,7 +5757,7 @@
         <v>0</v>
       </c>
       <c r="B666" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -5773,7 +5773,7 @@
         <v>0</v>
       </c>
       <c r="B668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -5789,7 +5789,7 @@
         <v>0</v>
       </c>
       <c r="B670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="671">
@@ -5813,7 +5813,7 @@
         <v>0</v>
       </c>
       <c r="B673" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="674">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="B678" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="679">
@@ -5869,7 +5869,7 @@
         <v>0</v>
       </c>
       <c r="B680" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="681">
@@ -5877,7 +5877,7 @@
         <v>0</v>
       </c>
       <c r="B681" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="682">
@@ -5909,7 +5909,7 @@
         <v>0</v>
       </c>
       <c r="B685" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="686">
@@ -5917,7 +5917,7 @@
         <v>0</v>
       </c>
       <c r="B686" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="687">
@@ -5941,7 +5941,7 @@
         <v>0</v>
       </c>
       <c r="B689" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="690">
@@ -5949,7 +5949,7 @@
         <v>0</v>
       </c>
       <c r="B690" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="691">
@@ -5965,7 +5965,7 @@
         <v>0</v>
       </c>
       <c r="B692" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="693">
@@ -5973,7 +5973,7 @@
         <v>0</v>
       </c>
       <c r="B693" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="694">
@@ -5981,7 +5981,7 @@
         <v>0</v>
       </c>
       <c r="B694" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="695">
@@ -5989,7 +5989,7 @@
         <v>0</v>
       </c>
       <c r="B695" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="696">
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="B696" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="697">
@@ -6005,7 +6005,7 @@
         <v>0</v>
       </c>
       <c r="B697" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="698">
@@ -6021,7 +6021,7 @@
         <v>0</v>
       </c>
       <c r="B699" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="700">
@@ -6037,7 +6037,7 @@
         <v>0</v>
       </c>
       <c r="B701" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="702">
@@ -6045,7 +6045,7 @@
         <v>0</v>
       </c>
       <c r="B702" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="703">
@@ -6053,7 +6053,7 @@
         <v>0</v>
       </c>
       <c r="B703" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="704">
@@ -6085,7 +6085,7 @@
         <v>0</v>
       </c>
       <c r="B707" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="708">
@@ -6093,7 +6093,7 @@
         <v>0</v>
       </c>
       <c r="B708" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="709">
@@ -6133,7 +6133,7 @@
         <v>0</v>
       </c>
       <c r="B713" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="714">
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="B717" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="718">
@@ -6173,7 +6173,7 @@
         <v>0</v>
       </c>
       <c r="B718" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="719">
@@ -6181,7 +6181,7 @@
         <v>0</v>
       </c>
       <c r="B719" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="720">
@@ -6213,7 +6213,7 @@
         <v>0</v>
       </c>
       <c r="B723" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="724">
@@ -6221,7 +6221,7 @@
         <v>0</v>
       </c>
       <c r="B724" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="725">
@@ -6253,7 +6253,7 @@
         <v>0</v>
       </c>
       <c r="B728" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="729">
@@ -6261,7 +6261,7 @@
         <v>0</v>
       </c>
       <c r="B729" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="730">
@@ -6285,7 +6285,7 @@
         <v>0</v>
       </c>
       <c r="B732" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="733">
@@ -6317,7 +6317,7 @@
         <v>0</v>
       </c>
       <c r="B736" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="737">
@@ -6325,7 +6325,7 @@
         <v>0</v>
       </c>
       <c r="B737" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="738">
@@ -6333,7 +6333,7 @@
         <v>0</v>
       </c>
       <c r="B738" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="739">
@@ -6341,7 +6341,7 @@
         <v>0</v>
       </c>
       <c r="B739" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="740">
@@ -6365,7 +6365,7 @@
         <v>0</v>
       </c>
       <c r="B742" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="743">
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="B743" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="744">
@@ -6381,7 +6381,7 @@
         <v>0</v>
       </c>
       <c r="B744" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="745">
@@ -6389,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="B745" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="746">
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="B747" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="748">
@@ -6429,7 +6429,7 @@
         <v>0</v>
       </c>
       <c r="B750" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="751">
@@ -6437,7 +6437,7 @@
         <v>0</v>
       </c>
       <c r="B751" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="752">
@@ -6453,7 +6453,7 @@
         <v>0</v>
       </c>
       <c r="B753" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="754">
@@ -6493,7 +6493,7 @@
         <v>0</v>
       </c>
       <c r="B758" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="759">
@@ -6501,7 +6501,7 @@
         <v>0</v>
       </c>
       <c r="B759" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="760">
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="B760" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="761">
@@ -6517,7 +6517,7 @@
         <v>0</v>
       </c>
       <c r="B761" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="762">
@@ -6533,7 +6533,7 @@
         <v>0</v>
       </c>
       <c r="B763" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="764">
@@ -6541,7 +6541,7 @@
         <v>0</v>
       </c>
       <c r="B764" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="765">
@@ -6565,7 +6565,7 @@
         <v>0</v>
       </c>
       <c r="B767" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="768">
@@ -6581,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="B769" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="770">
@@ -6589,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="B770" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="771">
@@ -6597,7 +6597,7 @@
         <v>0</v>
       </c>
       <c r="B771" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="772">
@@ -6605,7 +6605,7 @@
         <v>0</v>
       </c>
       <c r="B772" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="773">
@@ -6613,7 +6613,7 @@
         <v>0</v>
       </c>
       <c r="B773" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="774">
@@ -6629,7 +6629,7 @@
         <v>0</v>
       </c>
       <c r="B775" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="776">
@@ -6645,7 +6645,7 @@
         <v>0</v>
       </c>
       <c r="B777" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="778">
@@ -6653,7 +6653,7 @@
         <v>0</v>
       </c>
       <c r="B778" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="779">
@@ -6661,7 +6661,7 @@
         <v>0</v>
       </c>
       <c r="B779" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="780">
@@ -6669,7 +6669,7 @@
         <v>0</v>
       </c>
       <c r="B780" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="781">
@@ -6693,7 +6693,7 @@
         <v>0</v>
       </c>
       <c r="B783" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="784">
@@ -6701,7 +6701,7 @@
         <v>0</v>
       </c>
       <c r="B784" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="785">
@@ -6709,7 +6709,7 @@
         <v>0</v>
       </c>
       <c r="B785" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="786">
@@ -6717,7 +6717,7 @@
         <v>0</v>
       </c>
       <c r="B786" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="787">
@@ -6733,7 +6733,7 @@
         <v>0</v>
       </c>
       <c r="B788" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789">
@@ -6741,7 +6741,7 @@
         <v>0</v>
       </c>
       <c r="B789" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="790">
@@ -6749,7 +6749,7 @@
         <v>0</v>
       </c>
       <c r="B790" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="791">
@@ -6757,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="B791" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="792">
@@ -6805,7 +6805,7 @@
         <v>0</v>
       </c>
       <c r="B797" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="798">
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="B799" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="800">
@@ -6829,7 +6829,7 @@
         <v>0</v>
       </c>
       <c r="B800" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="801">
@@ -6837,7 +6837,7 @@
         <v>0</v>
       </c>
       <c r="B801" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="802">
@@ -6853,7 +6853,7 @@
         <v>0</v>
       </c>
       <c r="B803" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="804">
@@ -6861,7 +6861,7 @@
         <v>0</v>
       </c>
       <c r="B804" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="805">
@@ -6869,7 +6869,7 @@
         <v>0</v>
       </c>
       <c r="B805" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="806">
@@ -6909,7 +6909,7 @@
         <v>0</v>
       </c>
       <c r="B810" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="811">
@@ -6917,7 +6917,7 @@
         <v>0</v>
       </c>
       <c r="B811" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="812">
@@ -6941,7 +6941,7 @@
         <v>0</v>
       </c>
       <c r="B814" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="815">
@@ -6965,7 +6965,7 @@
         <v>0</v>
       </c>
       <c r="B817" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="818">
@@ -6981,7 +6981,7 @@
         <v>0</v>
       </c>
       <c r="B819" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="820">
@@ -6989,7 +6989,7 @@
         <v>0</v>
       </c>
       <c r="B820" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="821">
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="B821" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="822">
@@ -7029,7 +7029,7 @@
         <v>0</v>
       </c>
       <c r="B825" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="826">
@@ -7045,7 +7045,7 @@
         <v>0</v>
       </c>
       <c r="B827" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="828">
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="B828" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="829">
@@ -7061,7 +7061,7 @@
         <v>0</v>
       </c>
       <c r="B829" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="830">
@@ -7069,7 +7069,7 @@
         <v>0</v>
       </c>
       <c r="B830" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="831">
@@ -7085,7 +7085,7 @@
         <v>0</v>
       </c>
       <c r="B832" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="833">
@@ -7093,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="B833" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="834">
@@ -7101,7 +7101,7 @@
         <v>0</v>
       </c>
       <c r="B834" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="835">
@@ -7109,7 +7109,7 @@
         <v>0</v>
       </c>
       <c r="B835" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="836">
@@ -7117,7 +7117,7 @@
         <v>0</v>
       </c>
       <c r="B836" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="837">
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="B837" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="838">
@@ -7133,7 +7133,7 @@
         <v>0</v>
       </c>
       <c r="B838" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="839">
@@ -7141,7 +7141,7 @@
         <v>0</v>
       </c>
       <c r="B839" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="840">
@@ -7157,7 +7157,7 @@
         <v>0</v>
       </c>
       <c r="B841" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="842">
@@ -7165,7 +7165,7 @@
         <v>0</v>
       </c>
       <c r="B842" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="843">
@@ -7181,7 +7181,7 @@
         <v>0</v>
       </c>
       <c r="B844" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="845">
@@ -7189,7 +7189,7 @@
         <v>0</v>
       </c>
       <c r="B845" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846">
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="B847" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="848">
@@ -7213,7 +7213,7 @@
         <v>0</v>
       </c>
       <c r="B848" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="849">
@@ -7221,7 +7221,7 @@
         <v>0</v>
       </c>
       <c r="B849" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850">
@@ -7229,7 +7229,7 @@
         <v>0</v>
       </c>
       <c r="B850" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="851">
@@ -7269,7 +7269,7 @@
         <v>0</v>
       </c>
       <c r="B855" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="856">
@@ -7285,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="B857" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="858">
@@ -7293,7 +7293,7 @@
         <v>0</v>
       </c>
       <c r="B858" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="859">
@@ -7301,7 +7301,7 @@
         <v>0</v>
       </c>
       <c r="B859" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="860">
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="B860" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="861">
@@ -7317,7 +7317,7 @@
         <v>0</v>
       </c>
       <c r="B861" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="862">
@@ -7325,7 +7325,7 @@
         <v>0</v>
       </c>
       <c r="B862" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="863">
@@ -7333,7 +7333,7 @@
         <v>0</v>
       </c>
       <c r="B863" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="864">
@@ -7341,7 +7341,7 @@
         <v>0</v>
       </c>
       <c r="B864" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="865">
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="B865" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="866">
@@ -7365,7 +7365,7 @@
         <v>0</v>
       </c>
       <c r="B867" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="868">
@@ -7373,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="B868" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="869">
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="B869" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="870">
@@ -7389,7 +7389,7 @@
         <v>0</v>
       </c>
       <c r="B870" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="871">
@@ -7429,7 +7429,7 @@
         <v>0</v>
       </c>
       <c r="B875" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="876">
@@ -7445,7 +7445,7 @@
         <v>0</v>
       </c>
       <c r="B877" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="878">
@@ -7453,7 +7453,7 @@
         <v>0</v>
       </c>
       <c r="B878" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="879">
@@ -7461,7 +7461,7 @@
         <v>0</v>
       </c>
       <c r="B879" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="880">
@@ -7469,7 +7469,7 @@
         <v>0</v>
       </c>
       <c r="B880" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="881">
@@ -7501,7 +7501,7 @@
         <v>0</v>
       </c>
       <c r="B884" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="885">
@@ -7509,7 +7509,7 @@
         <v>0</v>
       </c>
       <c r="B885" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="886">
@@ -7525,7 +7525,7 @@
         <v>0</v>
       </c>
       <c r="B887" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="888">
@@ -7533,7 +7533,7 @@
         <v>0</v>
       </c>
       <c r="B888" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="889">
@@ -7541,7 +7541,7 @@
         <v>0</v>
       </c>
       <c r="B889" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="890">
@@ -7565,7 +7565,7 @@
         <v>0</v>
       </c>
       <c r="B892" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="893">
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="B893" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="894">
@@ -7581,7 +7581,7 @@
         <v>0</v>
       </c>
       <c r="B894" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="895">
@@ -7589,7 +7589,7 @@
         <v>0</v>
       </c>
       <c r="B895" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="896">
@@ -7597,7 +7597,7 @@
         <v>0</v>
       </c>
       <c r="B896" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="897">
@@ -7613,7 +7613,7 @@
         <v>0</v>
       </c>
       <c r="B898" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="899">
@@ -7621,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="B899" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="900">
@@ -7637,7 +7637,7 @@
         <v>0</v>
       </c>
       <c r="B901" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="902">
@@ -7653,7 +7653,7 @@
         <v>0</v>
       </c>
       <c r="B903" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="904">
@@ -7661,7 +7661,7 @@
         <v>0</v>
       </c>
       <c r="B904" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="905">
@@ -7669,7 +7669,7 @@
         <v>0</v>
       </c>
       <c r="B905" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="906">
@@ -7677,7 +7677,7 @@
         <v>0</v>
       </c>
       <c r="B906" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="907">
@@ -7709,7 +7709,7 @@
         <v>0</v>
       </c>
       <c r="B910" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="911">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="B912" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="913">
@@ -7733,7 +7733,7 @@
         <v>0</v>
       </c>
       <c r="B913" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="914">
@@ -7757,7 +7757,7 @@
         <v>0</v>
       </c>
       <c r="B916" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="917">
@@ -7765,7 +7765,7 @@
         <v>0</v>
       </c>
       <c r="B917" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="918">
@@ -7789,7 +7789,7 @@
         <v>0</v>
       </c>
       <c r="B920" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="921">
@@ -7805,7 +7805,7 @@
         <v>0</v>
       </c>
       <c r="B922" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="923">
@@ -7813,7 +7813,7 @@
         <v>0</v>
       </c>
       <c r="B923" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924">
@@ -7821,7 +7821,7 @@
         <v>0</v>
       </c>
       <c r="B924" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="925">
@@ -7837,7 +7837,7 @@
         <v>0</v>
       </c>
       <c r="B926" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="927">
@@ -7861,7 +7861,7 @@
         <v>0</v>
       </c>
       <c r="B929" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="930">
@@ -7877,7 +7877,7 @@
         <v>0</v>
       </c>
       <c r="B931" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="932">
@@ -7901,7 +7901,7 @@
         <v>0</v>
       </c>
       <c r="B934" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="935">
@@ -7925,7 +7925,7 @@
         <v>0</v>
       </c>
       <c r="B937" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="938">
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="B938" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="939">
@@ -7941,7 +7941,7 @@
         <v>0</v>
       </c>
       <c r="B939" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="940">
@@ -7957,7 +7957,7 @@
         <v>0</v>
       </c>
       <c r="B941" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="942">
@@ -7965,7 +7965,7 @@
         <v>0</v>
       </c>
       <c r="B942" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="943">
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="B943" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="944">
@@ -7981,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="B944" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="945">
@@ -7997,7 +7997,7 @@
         <v>0</v>
       </c>
       <c r="B946" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="947">
@@ -8005,7 +8005,7 @@
         <v>0</v>
       </c>
       <c r="B947" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="948">
@@ -8013,7 +8013,7 @@
         <v>0</v>
       </c>
       <c r="B948" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="949">
@@ -8021,7 +8021,7 @@
         <v>0</v>
       </c>
       <c r="B949" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="950">
@@ -8029,7 +8029,7 @@
         <v>0</v>
       </c>
       <c r="B950" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="951">
@@ -8045,7 +8045,7 @@
         <v>0</v>
       </c>
       <c r="B952" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="953">
@@ -8061,7 +8061,7 @@
         <v>0</v>
       </c>
       <c r="B954" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="955">
@@ -8085,7 +8085,7 @@
         <v>0</v>
       </c>
       <c r="B957" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="958">
@@ -8101,7 +8101,7 @@
         <v>0</v>
       </c>
       <c r="B959" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="960">
@@ -8109,7 +8109,7 @@
         <v>0</v>
       </c>
       <c r="B960" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="961">
@@ -8125,7 +8125,7 @@
         <v>0</v>
       </c>
       <c r="B962" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="963">
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="B964" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="965">
@@ -8149,7 +8149,7 @@
         <v>0</v>
       </c>
       <c r="B965" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="966">
@@ -8157,7 +8157,7 @@
         <v>0</v>
       </c>
       <c r="B966" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="967">
@@ -8165,7 +8165,7 @@
         <v>0</v>
       </c>
       <c r="B967" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="968">
@@ -8173,7 +8173,7 @@
         <v>0</v>
       </c>
       <c r="B968" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="969">
@@ -8181,7 +8181,7 @@
         <v>0</v>
       </c>
       <c r="B969" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="970">
@@ -8205,7 +8205,7 @@
         <v>0</v>
       </c>
       <c r="B972" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="973">
@@ -8213,7 +8213,7 @@
         <v>0</v>
       </c>
       <c r="B973" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="974">
@@ -8221,7 +8221,7 @@
         <v>0</v>
       </c>
       <c r="B974" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="975">
@@ -8237,7 +8237,7 @@
         <v>0</v>
       </c>
       <c r="B976" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="977">
@@ -8261,7 +8261,7 @@
         <v>0</v>
       </c>
       <c r="B979" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="980">
@@ -8269,7 +8269,7 @@
         <v>0</v>
       </c>
       <c r="B980" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="981">
@@ -8277,7 +8277,7 @@
         <v>0</v>
       </c>
       <c r="B981" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="982">
@@ -8293,7 +8293,7 @@
         <v>0</v>
       </c>
       <c r="B983" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="984">
@@ -8309,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="B985" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="986">
@@ -8325,7 +8325,7 @@
         <v>0</v>
       </c>
       <c r="B987" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="988">
@@ -8341,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="B989" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="990">
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="B990" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="991">
@@ -8357,7 +8357,7 @@
         <v>0</v>
       </c>
       <c r="B991" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="992">
@@ -8365,7 +8365,7 @@
         <v>0</v>
       </c>
       <c r="B992" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="993">
@@ -8373,7 +8373,7 @@
         <v>0</v>
       </c>
       <c r="B993" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="994">
@@ -8381,7 +8381,7 @@
         <v>0</v>
       </c>
       <c r="B994" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="995">
@@ -8389,7 +8389,7 @@
         <v>0</v>
       </c>
       <c r="B995" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="996">
@@ -8397,7 +8397,7 @@
         <v>0</v>
       </c>
       <c r="B996" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="997">
@@ -8421,7 +8421,7 @@
         <v>0</v>
       </c>
       <c r="B999" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1000">
@@ -8429,7 +8429,7 @@
         <v>0</v>
       </c>
       <c r="B1000" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1001">
@@ -8469,7 +8469,7 @@
         <v>1</v>
       </c>
       <c r="B1005" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1006">
@@ -8477,7 +8477,7 @@
         <v>1</v>
       </c>
       <c r="B1006" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1007">
@@ -8485,7 +8485,7 @@
         <v>1</v>
       </c>
       <c r="B1007" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1008">
@@ -8509,7 +8509,7 @@
         <v>1</v>
       </c>
       <c r="B1010" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1011">
@@ -8517,7 +8517,7 @@
         <v>1</v>
       </c>
       <c r="B1011" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1012">
@@ -8525,7 +8525,7 @@
         <v>1</v>
       </c>
       <c r="B1012" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1013">
@@ -8541,7 +8541,7 @@
         <v>1</v>
       </c>
       <c r="B1014" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1015">
@@ -8565,7 +8565,7 @@
         <v>1</v>
       </c>
       <c r="B1017" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1018">
@@ -8613,7 +8613,7 @@
         <v>1</v>
       </c>
       <c r="B1023" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1024">
@@ -8629,7 +8629,7 @@
         <v>1</v>
       </c>
       <c r="B1025" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1026">
@@ -8653,7 +8653,7 @@
         <v>1</v>
       </c>
       <c r="B1028" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1029">
@@ -8685,7 +8685,7 @@
         <v>1</v>
       </c>
       <c r="B1032" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1033">
@@ -8693,7 +8693,7 @@
         <v>1</v>
       </c>
       <c r="B1033" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1034">
@@ -8709,7 +8709,7 @@
         <v>1</v>
       </c>
       <c r="B1035" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1036">
@@ -8717,7 +8717,7 @@
         <v>1</v>
       </c>
       <c r="B1036" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1037">
@@ -8733,7 +8733,7 @@
         <v>1</v>
       </c>
       <c r="B1038" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1039">
@@ -8757,7 +8757,7 @@
         <v>1</v>
       </c>
       <c r="B1041" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1042">
@@ -8773,7 +8773,7 @@
         <v>1</v>
       </c>
       <c r="B1043" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1044">
@@ -8813,7 +8813,7 @@
         <v>1</v>
       </c>
       <c r="B1048" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1049">
@@ -8821,7 +8821,7 @@
         <v>1</v>
       </c>
       <c r="B1049" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1050">
@@ -8829,7 +8829,7 @@
         <v>1</v>
       </c>
       <c r="B1050" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1051">
@@ -8837,7 +8837,7 @@
         <v>1</v>
       </c>
       <c r="B1051" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1052">
@@ -8845,7 +8845,7 @@
         <v>1</v>
       </c>
       <c r="B1052" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1053">
@@ -8853,7 +8853,7 @@
         <v>1</v>
       </c>
       <c r="B1053" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1054">
@@ -8861,7 +8861,7 @@
         <v>1</v>
       </c>
       <c r="B1054" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1055">
@@ -8869,7 +8869,7 @@
         <v>1</v>
       </c>
       <c r="B1055" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1056">
@@ -8941,7 +8941,7 @@
         <v>1</v>
       </c>
       <c r="B1064" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1065">
@@ -8957,7 +8957,7 @@
         <v>1</v>
       </c>
       <c r="B1066" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1067">
